--- a/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
   <si>
     <t>ITOCY</t>
   </si>
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -656,63 +656,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -740,8 +743,11 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -769,8 +775,11 @@
       <c r="K9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -798,8 +807,11 @@
       <c r="K10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,8 +823,9 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -840,8 +853,11 @@
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,8 +885,11 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -898,8 +917,11 @@
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -927,8 +949,11 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,8 +962,9 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -966,8 +992,11 @@
       <c r="K17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -995,8 +1024,11 @@
       <c r="K18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1008,8 +1040,9 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1037,8 +1070,11 @@
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1066,8 +1102,11 @@
       <c r="K21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1095,8 +1134,11 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1124,8 +1166,11 @@
       <c r="K23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1153,8 +1198,11 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1182,8 +1230,11 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1211,8 +1262,11 @@
       <c r="K26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1240,8 +1294,11 @@
       <c r="K27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1269,8 +1326,11 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1298,8 +1358,11 @@
       <c r="K29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1327,8 +1390,11 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1356,8 +1422,11 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1385,8 +1454,11 @@
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1414,8 +1486,11 @@
       <c r="K33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1443,8 +1518,11 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1472,42 +1550,48 @@
       <c r="K35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1519,8 +1603,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1532,269 +1617,297 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3579400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4172100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3710200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3969700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4101400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4061200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4271800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4558700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4029200</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>666100</v>
+      </c>
+      <c r="E42" s="3">
         <v>597600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>794400</v>
-      </c>
-      <c r="F42" s="3">
-        <v>586000</v>
       </c>
       <c r="G42" s="3">
         <v>586000</v>
       </c>
       <c r="H42" s="3">
+        <v>586000</v>
+      </c>
+      <c r="I42" s="3">
         <v>729100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>759000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>622900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>852800</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>21434400</v>
+      </c>
+      <c r="E43" s="3">
         <v>20501000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20517100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20003100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23059300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>21026800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>19978000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>20325100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23554900</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10408900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10175500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9176700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9138000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10578300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9065500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9042000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9816500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11183100</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3457500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3280900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3261700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3483900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2845400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2770300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2743800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3202500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2929600</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>39546300</v>
+      </c>
+      <c r="E46" s="3">
         <v>38727200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37460100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37180600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>41170300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37652900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36794600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38525600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>42549500</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>30411900</v>
+      </c>
+      <c r="E47" s="3">
         <v>30724300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>28220600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28776700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29755500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>27968100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27639400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28375900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28232800</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13961200</v>
+      </c>
+      <c r="E48" s="3">
         <v>14651500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13412900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13954000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14515000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13606600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13909500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15033700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15201700</v>
       </c>
     </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8013500</v>
+      </c>
+      <c r="E49" s="3">
         <v>7780600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7086000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7459600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7935300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7386900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7614300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8118700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8526600</v>
       </c>
     </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1822,8 +1935,11 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1851,37 +1967,43 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7805100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8108300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7723200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2038600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8056000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7842900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8013100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2183900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8230600</v>
       </c>
     </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1909,37 +2031,43 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>100130900</v>
+      </c>
+      <c r="E54" s="3">
         <v>100436500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>94309600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95796500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>101868500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>94868100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>94355500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>98661000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>103123200</v>
       </c>
     </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1951,8 +2079,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -1964,182 +2093,201 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17041800</v>
+      </c>
+      <c r="E57" s="3">
         <v>15953400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15625600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15491100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17999700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16249100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14709300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15365600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18650700</v>
       </c>
     </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6788000</v>
+      </c>
+      <c r="E58" s="3">
         <v>6484600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6503200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6294400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7603200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6504600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6807200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6755200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7089700</v>
       </c>
     </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6913500</v>
+      </c>
+      <c r="E59" s="3">
         <v>7045000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6830700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6923500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8130800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6719800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6930700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7554300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7801500</v>
       </c>
     </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30743300</v>
+      </c>
+      <c r="E60" s="3">
         <v>29483000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28959500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28709000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33733600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29473400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28447100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>29675100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33542000</v>
       </c>
     </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23863100</v>
+      </c>
+      <c r="E61" s="3">
         <v>23282700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>21690000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>22770400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>23006000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21963600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21629200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>23419200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23992300</v>
       </c>
     </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1662300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1557600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1527000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1568100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1618600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1551000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1565400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1654400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1801800</v>
       </c>
     </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2167,8 +2315,11 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2196,8 +2347,11 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2225,37 +2379,43 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59649400</v>
+      </c>
+      <c r="E66" s="3">
         <v>57613100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55252200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>56180500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61647200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55956400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54475300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57532500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62211600</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2267,8 +2427,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2296,8 +2457,11 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2325,8 +2489,11 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2354,8 +2521,11 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2383,37 +2553,43 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>34808200</v>
+      </c>
+      <c r="E72" s="3">
         <v>37326400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>31786800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>33268600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>34208800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>31724100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31338700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33358400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32665800</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2441,8 +2617,11 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2470,8 +2649,11 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2499,37 +2681,43 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>36877800</v>
+      </c>
+      <c r="E76" s="3">
         <v>39057100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35507200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35879600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>36257300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>34893900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35342100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36283100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35877800</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2557,42 +2745,48 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2620,8 +2814,11 @@
       <c r="K81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2633,37 +2830,41 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>748800</v>
+      </c>
+      <c r="E83" s="3">
         <v>700200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>423700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>781100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>699900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>733600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>432700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>872800</v>
       </c>
     </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2691,8 +2892,11 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2720,8 +2924,11 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2749,8 +2956,11 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2778,8 +2988,11 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2807,37 +3020,43 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2588300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1291600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2326000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1114300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1708400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1480400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2270600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1267000</v>
       </c>
     </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2849,37 +3068,41 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-319000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-248600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-365500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-710100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-275100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-226100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-156300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-502200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-298600</v>
       </c>
     </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2907,8 +3130,11 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -2936,37 +3162,43 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2024300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-449700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-609400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-341900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-451000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-279200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-338900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-125800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-987800</v>
       </c>
     </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -2978,37 +3210,41 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>912000</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>716300</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>824300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>755700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>725400</v>
       </c>
     </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3036,8 +3272,11 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3065,8 +3304,11 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3094,91 +3336,103 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>920100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1982900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-795200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1906200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-815000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1543000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1158500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1587300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-857500</v>
       </c>
     </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-50100</v>
+      </c>
+      <c r="E101" s="3">
         <v>39800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>97600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-112600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>53000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>123300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>181800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>73800</v>
       </c>
     </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-222400</v>
+      </c>
+      <c r="E102" s="3">
         <v>6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-22300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>147400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-201800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-74000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>80500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>561600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-691000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
   <si>
     <t>ITOCY</t>
   </si>
@@ -656,66 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -746,8 +749,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -778,8 +784,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -810,8 +819,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,8 +869,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,8 +904,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -920,8 +939,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -952,8 +974,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -963,8 +988,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -995,8 +1021,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1027,8 +1056,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1041,8 +1073,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1073,8 +1106,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1105,8 +1141,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1137,8 +1176,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1169,8 +1211,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1201,8 +1246,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1233,8 +1281,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1265,8 +1316,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1297,8 +1351,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1329,8 +1386,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,8 +1421,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1393,8 +1456,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1425,8 +1491,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1457,8 +1526,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1489,8 +1561,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1521,8 +1596,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1553,45 +1631,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1604,8 +1688,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1618,296 +1703,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3670000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3579400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4172100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3710200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3969700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4101400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4061200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4271800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4558700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4029200</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>583200</v>
+      </c>
+      <c r="E42" s="3">
         <v>666100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>597600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>794400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>586000</v>
       </c>
       <c r="H42" s="3">
         <v>586000</v>
       </c>
       <c r="I42" s="3">
+        <v>586000</v>
+      </c>
+      <c r="J42" s="3">
         <v>729100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>759000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>622900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>852800</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20543800</v>
+      </c>
+      <c r="E43" s="3">
         <v>21434400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20501000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20517100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20003100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23059300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21026800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19978000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20325100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>23554900</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9898900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10408900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10175500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9176700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9138000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10578300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9065500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9042000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9816500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11183100</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3527000</v>
+      </c>
+      <c r="E45" s="3">
         <v>3457500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3280900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3261700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3483900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2845400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2770300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2743800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3202500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2929600</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38222900</v>
+      </c>
+      <c r="E46" s="3">
         <v>39546300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38727200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37460100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>37180600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>41170300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>37652900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>36794600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38525600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42549500</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31498300</v>
+      </c>
+      <c r="E47" s="3">
         <v>30411900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>30724300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>28220600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>28776700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29755500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27968100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>27639400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>28375900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28232800</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14901000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13961200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14651500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13412900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13954000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14515000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13606600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13909500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15033700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15201700</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8076200</v>
+      </c>
+      <c r="E49" s="3">
         <v>8013500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7780600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>7086000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7459600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7935300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7386900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7614300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8118700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8526600</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1938,8 +2051,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1970,40 +2086,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7903700</v>
+      </c>
+      <c r="E52" s="3">
         <v>7805100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8108300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7723200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2038600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>8056000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7842900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8013100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2183900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8230600</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2034,40 +2156,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>101064900</v>
+      </c>
+      <c r="E54" s="3">
         <v>100130900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100436500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>94309600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95796500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>101868500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>94868100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>94355500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>98661000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>103123200</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2080,8 +2208,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2094,200 +2223,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15108400</v>
+      </c>
+      <c r="E57" s="3">
         <v>17041800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15953400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15625600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15491100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17999700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16249100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14709300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15365600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18650700</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7094900</v>
+      </c>
+      <c r="E58" s="3">
         <v>6788000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6484600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6503200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6294400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7603200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6504600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6807200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6755200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7089700</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7757600</v>
+      </c>
+      <c r="E59" s="3">
         <v>6913500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7045000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6830700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6923500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8130800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6719800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6930700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7554300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7801500</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29960900</v>
+      </c>
+      <c r="E60" s="3">
         <v>30743300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29483000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28959500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28709000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33733600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>29473400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28447100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29675100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33542000</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>23768300</v>
+      </c>
+      <c r="E61" s="3">
         <v>23863100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>23282700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>21690000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22770400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23006000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>21963600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>21629200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>23419200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23992300</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1798500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1662300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1557600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1527000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1568100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1618600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1551000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1565400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1654400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1801800</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2318,8 +2466,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2350,8 +2501,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2382,40 +2536,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59056200</v>
+      </c>
+      <c r="E66" s="3">
         <v>59649400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57613100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55252200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>56180500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61647200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55956400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54475300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57532500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>62211600</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2428,8 +2588,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2460,8 +2621,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2492,8 +2656,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2524,8 +2691,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2556,40 +2726,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>37785400</v>
+      </c>
+      <c r="E72" s="3">
         <v>34808200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>37326400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>31786800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>33268600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>34208800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>31724100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>31338700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33358400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>32665800</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2620,8 +2796,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2652,8 +2831,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2684,40 +2866,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38431700</v>
+      </c>
+      <c r="E76" s="3">
         <v>36877800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39057100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35507200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35879600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36257300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>34893900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35342100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36283100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35877800</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2748,45 +2936,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2817,8 +3011,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2831,40 +3028,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>376000</v>
+      </c>
+      <c r="E83" s="3">
         <v>748800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>700200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>423700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>781100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>699900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>733600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>432700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>872800</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2895,8 +3096,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2927,8 +3131,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2959,8 +3166,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2991,8 +3201,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3023,40 +3236,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1943500</v>
+      </c>
+      <c r="E89" s="3">
         <v>812000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2588300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1291600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2326000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1114300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1708400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1480400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2270600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1267000</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3069,40 +3288,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-321000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-319000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-248600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-365500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-710100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-275100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-226100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-156300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-502200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-298600</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3133,8 +3356,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3165,40 +3391,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-237300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2024300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-449700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-609400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-341900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-451000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-279200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-338900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-125800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-987800</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3211,40 +3443,44 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>912000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>716300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>824300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>755700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>725400</v>
       </c>
     </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3275,8 +3511,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3307,8 +3546,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3339,100 +3581,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1720700</v>
+      </c>
+      <c r="E100" s="3">
         <v>920100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1982900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-795200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1906200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-815000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1543000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1158500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1587300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-857500</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-50100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>39800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>97600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-112600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>53000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>123300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>181800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>73800</v>
       </c>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-88000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-222400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-22300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>147400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-201800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-74000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>80500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>561600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-691000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ITOCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="92">
   <si>
     <t>ITOCY</t>
   </si>
@@ -656,69 +656,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -752,8 +755,11 @@
       <c r="M8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -787,8 +793,11 @@
       <c r="M9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +831,11 @@
       <c r="M10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,8 +885,11 @@
       <c r="M12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,8 +923,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -942,8 +961,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,8 +999,11 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -989,8 +1014,9 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1050,11 @@
       <c r="M17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1059,8 +1088,11 @@
       <c r="M18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1074,8 +1106,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1109,8 +1142,11 @@
       <c r="M20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1144,8 +1180,11 @@
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1179,8 +1218,11 @@
       <c r="M22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1214,8 +1256,11 @@
       <c r="M23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1249,8 +1294,11 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1284,8 +1332,11 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1319,8 +1370,11 @@
       <c r="M26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1354,8 +1408,11 @@
       <c r="M27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1389,8 +1446,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1424,8 +1484,11 @@
       <c r="M29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1459,8 +1522,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1494,8 +1560,11 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1529,8 +1598,11 @@
       <c r="M32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1564,8 +1636,11 @@
       <c r="M33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1674,11 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1634,48 +1712,54 @@
       <c r="M35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1689,8 +1773,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1704,323 +1789,351 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3702000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3670000</v>
       </c>
-      <c r="E41" s="3">
-        <v>3579400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>4172100</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
         <v>3710200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3969700</v>
       </c>
-      <c r="I41" s="3">
-        <v>4101400</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3">
         <v>4061200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4271800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4558700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4029200</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>597500</v>
+      </c>
+      <c r="E42" s="3">
         <v>583200</v>
       </c>
-      <c r="E42" s="3">
-        <v>666100</v>
-      </c>
       <c r="F42" s="3">
-        <v>597600</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>794400</v>
-      </c>
-      <c r="H42" s="3">
-        <v>586000</v>
       </c>
       <c r="I42" s="3">
         <v>586000</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>729100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>759000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>622900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>852800</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20543800</v>
+        <v>21518800</v>
       </c>
       <c r="E43" s="3">
-        <v>21434400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>20501000</v>
-      </c>
-      <c r="G43" s="3">
+        <v>20152600</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>20517100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20003100</v>
       </c>
-      <c r="I43" s="3">
-        <v>23059300</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
         <v>21026800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19978000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20325100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>23554900</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10690300</v>
+      </c>
+      <c r="E44" s="3">
         <v>9898900</v>
       </c>
-      <c r="E44" s="3">
-        <v>10408900</v>
-      </c>
-      <c r="F44" s="3">
-        <v>10175500</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>9176700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9138000</v>
       </c>
-      <c r="I44" s="3">
-        <v>10578300</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K44" s="3">
         <v>9065500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9042000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9816500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11183100</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3527000</v>
+        <v>3910000</v>
       </c>
       <c r="E45" s="3">
-        <v>3457500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>3280900</v>
-      </c>
-      <c r="G45" s="3">
+        <v>3918200</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>3261700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3483900</v>
       </c>
-      <c r="I45" s="3">
-        <v>2845400</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>2770300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2743800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3202500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2929600</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40418700</v>
+      </c>
+      <c r="E46" s="3">
         <v>38222900</v>
       </c>
-      <c r="E46" s="3">
-        <v>39546300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>38727200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>37460100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>37180600</v>
       </c>
-      <c r="I46" s="3">
-        <v>41170300</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K46" s="3">
         <v>37652900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>36794600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>38525600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>42549500</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>32472900</v>
+      </c>
+      <c r="E47" s="3">
         <v>31498300</v>
       </c>
-      <c r="E47" s="3">
-        <v>30411900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>30724300</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>28220600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28776700</v>
       </c>
-      <c r="I47" s="3">
-        <v>29755500</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
         <v>27968100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>27639400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>28375900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28232800</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15403600</v>
+      </c>
+      <c r="E48" s="3">
         <v>14901000</v>
       </c>
-      <c r="E48" s="3">
-        <v>13961200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>14651500</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>13412900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13954000</v>
       </c>
-      <c r="I48" s="3">
-        <v>14515000</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
         <v>13606600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13909500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>15033700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>15201700</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8420000</v>
+      </c>
+      <c r="E49" s="3">
         <v>8076200</v>
       </c>
-      <c r="E49" s="3">
-        <v>8013500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>7780600</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="F49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" s="3">
         <v>7086000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7459600</v>
       </c>
-      <c r="I49" s="3">
-        <v>7935300</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="J49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K49" s="3">
         <v>7386900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7614300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8118700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8526600</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2054,8 +2167,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2089,43 +2205,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7903700</v>
+        <v>8055000</v>
       </c>
       <c r="E52" s="3">
-        <v>7805100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>8108300</v>
-      </c>
-      <c r="G52" s="3">
+        <v>1949600</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>7723200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2038600</v>
       </c>
-      <c r="I52" s="3">
-        <v>8056000</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
         <v>7842900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8013100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2183900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8230600</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2159,43 +2281,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>105201800</v>
+      </c>
+      <c r="E54" s="3">
         <v>101064900</v>
       </c>
-      <c r="E54" s="3">
-        <v>100130900</v>
-      </c>
-      <c r="F54" s="3">
-        <v>100436500</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>94309600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>95796500</v>
       </c>
-      <c r="I54" s="3">
-        <v>101868500</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
         <v>94868100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>94355500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>98661000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>103123200</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2209,8 +2337,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,218 +2353,237 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16081800</v>
+      </c>
+      <c r="E57" s="3">
         <v>15108400</v>
       </c>
-      <c r="E57" s="3">
-        <v>17041800</v>
-      </c>
-      <c r="F57" s="3">
-        <v>15953400</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>15625600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15491100</v>
       </c>
-      <c r="I57" s="3">
-        <v>17999700</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K57" s="3">
         <v>16249100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14709300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15365600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18650700</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7236000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7094900</v>
       </c>
-      <c r="E58" s="3">
-        <v>6788000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>6484600</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H58" s="3">
         <v>6503200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6294400</v>
       </c>
-      <c r="I58" s="3">
-        <v>7603200</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="J58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3">
         <v>6504600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6807200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6755200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7089700</v>
       </c>
     </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8090000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7757600</v>
       </c>
-      <c r="E59" s="3">
-        <v>6913500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>7045000</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>6830700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6923500</v>
       </c>
-      <c r="I59" s="3">
-        <v>8130800</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
         <v>6719800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6930700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7554300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7801500</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>31407900</v>
+      </c>
+      <c r="E60" s="3">
         <v>29960900</v>
       </c>
-      <c r="E60" s="3">
-        <v>30743300</v>
-      </c>
-      <c r="F60" s="3">
-        <v>29483000</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>28959500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>28709000</v>
       </c>
-      <c r="I60" s="3">
-        <v>33733600</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K60" s="3">
         <v>29473400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28447100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29675100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33542000</v>
       </c>
     </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24759200</v>
+      </c>
+      <c r="E61" s="3">
         <v>23768300</v>
       </c>
-      <c r="E61" s="3">
-        <v>23863100</v>
-      </c>
       <c r="F61" s="3">
-        <v>23282700</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>21690000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22770400</v>
       </c>
-      <c r="I61" s="3">
-        <v>23006000</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>21963600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21629200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>23419200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23992300</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1849100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1798500</v>
       </c>
-      <c r="E62" s="3">
-        <v>1662300</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1557600</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>1527000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1568100</v>
       </c>
-      <c r="I62" s="3">
-        <v>1618600</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>1551000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1565400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1654400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1801800</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2469,8 +2617,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2504,8 +2655,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2539,43 +2693,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61718400</v>
+      </c>
+      <c r="E66" s="3">
         <v>59056200</v>
       </c>
-      <c r="E66" s="3">
-        <v>59649400</v>
-      </c>
-      <c r="F66" s="3">
-        <v>57613100</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>55252200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>56180500</v>
       </c>
-      <c r="I66" s="3">
-        <v>61647200</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3">
         <v>55956400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54475300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57532500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62211600</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2589,8 +2749,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2624,8 +2785,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2659,8 +2823,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2694,8 +2861,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2729,43 +2899,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>40216200</v>
+      </c>
+      <c r="E72" s="3">
         <v>37785400</v>
       </c>
-      <c r="E72" s="3">
-        <v>34808200</v>
-      </c>
-      <c r="F72" s="3">
-        <v>37326400</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>31786800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33268600</v>
       </c>
-      <c r="I72" s="3">
-        <v>34208800</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
         <v>31724100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>31338700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33358400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32665800</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2799,8 +2975,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2834,8 +3013,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2869,43 +3051,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>39797200</v>
+      </c>
+      <c r="E76" s="3">
         <v>38431700</v>
       </c>
-      <c r="E76" s="3">
-        <v>36877800</v>
-      </c>
-      <c r="F76" s="3">
-        <v>39057100</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>35507200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35879600</v>
       </c>
-      <c r="I76" s="3">
-        <v>36257300</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K76" s="3">
         <v>34893900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35342100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>36283100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>35877800</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2939,48 +3127,54 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3014,8 +3208,11 @@
       <c r="M81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3029,43 +3226,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>683600</v>
+      </c>
+      <c r="E83" s="3">
         <v>376000</v>
       </c>
-      <c r="E83" s="3">
-        <v>748800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>700200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>700000</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
         <v>423700</v>
       </c>
-      <c r="I83" s="3">
-        <v>781100</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
         <v>699900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>733600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>432700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>872800</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3099,8 +3300,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3134,8 +3338,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3169,8 +3376,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3204,8 +3414,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3239,43 +3452,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1701600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1943500</v>
       </c>
-      <c r="E89" s="3">
-        <v>812000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>2588300</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" s="3">
         <v>1291600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2326000</v>
       </c>
-      <c r="I89" s="3">
-        <v>1114300</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
         <v>1708400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1480400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2270600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1267000</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3289,43 +3508,47 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-321000</v>
+        <v>-387100</v>
       </c>
       <c r="E91" s="3">
-        <v>-319000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-248600</v>
-      </c>
-      <c r="G91" s="3">
+        <v>-553600</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" s="3">
         <v>-365500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-710100</v>
       </c>
-      <c r="I91" s="3">
-        <v>-275100</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K91" s="3">
         <v>-226100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-156300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-502200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-298600</v>
       </c>
     </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3359,8 +3582,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3394,43 +3620,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-336200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-237300</v>
       </c>
-      <c r="E94" s="3">
-        <v>-2024300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-449700</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" s="3">
         <v>-609400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-341900</v>
       </c>
-      <c r="I94" s="3">
-        <v>-451000</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K94" s="3">
         <v>-279200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-338900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-125800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-987800</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3444,43 +3676,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>983900</v>
       </c>
       <c r="E96" s="3">
-        <v>912000</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3">
         <v>716300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
-        <v>824300</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>755700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>725400</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3514,8 +3750,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3549,8 +3788,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3584,109 +3826,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1460000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1720700</v>
       </c>
-      <c r="E100" s="3">
-        <v>920100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-1982900</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H100" s="3">
         <v>-795200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1906200</v>
       </c>
-      <c r="I100" s="3">
-        <v>-815000</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1543000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1158500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1587300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-857500</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E101" s="3">
         <v>69500</v>
       </c>
-      <c r="E101" s="3">
-        <v>-50100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>39800</v>
-      </c>
-      <c r="G101" s="3">
-        <v>97600</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3">
         <v>4100</v>
       </c>
-      <c r="I101" s="3">
-        <v>-112600</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K101" s="3">
         <v>53000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>123300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>181800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>73800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-107100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-88000</v>
       </c>
-      <c r="E102" s="3">
-        <v>-222400</v>
-      </c>
       <c r="F102" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-22300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>147400</v>
       </c>
-      <c r="I102" s="3">
-        <v>-201800</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-74000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>80500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>561600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-691000</v>
       </c>
     </row>
